--- a/load-tests/reports/baseline-load-test-report-400.xlsx
+++ b/load-tests/reports/baseline-load-test-report-400.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>12000</v>
+        <v>115803</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>200</v>
+        <v>1930.05</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>200</v>
+        <v>1930.05</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>11.96</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>19</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>11.96</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>200</v>
+        <v>1930.05</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/baseline-load-test-report-400.xlsx
+++ b/load-tests/reports/baseline-load-test-report-400.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>115803</v>
+        <v>133238</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>1930.05</v>
+        <v>2220.63</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>1930.05</v>
+        <v>2220.63</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>51.82</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>182</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>51.82</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>182</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>1930.05</v>
+        <v>2220.63</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/baseline-load-test-report-400.xlsx
+++ b/load-tests/reports/baseline-load-test-report-400.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>133238</v>
+        <v>16459</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>2220.63</v>
+        <v>274.32</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>2220.63</v>
+        <v>274.32</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>45.04</v>
+        <v>365.85</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>32</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>251</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>43</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>55</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>81</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>45.04</v>
+        <v>365.85</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>251</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>43</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>55</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>81</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>2220.63</v>
+        <v>274.32</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/baseline-load-test-report-400.xlsx
+++ b/load-tests/reports/baseline-load-test-report-400.xlsx
@@ -438,7 +438,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>16459</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="6">
@@ -454,7 +454,7 @@
         <v>Requests Per Second</v>
       </c>
       <c r="B7">
-        <v>274.32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -462,7 +462,7 @@
         <v>Throughput (req/sec)</v>
       </c>
       <c r="B8">
-        <v>274.32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>365.85</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +478,7 @@
         <v>Min Response Time (ms)</v>
       </c>
       <c r="B10">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -486,7 +486,7 @@
         <v>Max Response Time (ms)</v>
       </c>
       <c r="B11">
-        <v>1391</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -494,7 +494,7 @@
         <v>P50 Response Time (ms)</v>
       </c>
       <c r="B12">
-        <v>362</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>P95 Response Time (ms)</v>
       </c>
       <c r="B13">
-        <v>436</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -510,7 +510,7 @@
         <v>P99 Response Time (ms)</v>
       </c>
       <c r="B14">
-        <v>466</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>365.85</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>Minimum Response Time</v>
       </c>
       <c r="B3">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Maximum Response Time</v>
       </c>
       <c r="B4">
-        <v>1391</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>P50</v>
       </c>
       <c r="B5">
-        <v>362</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         <v>P95</v>
       </c>
       <c r="B6">
-        <v>436</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         <v>P99</v>
       </c>
       <c r="B7">
-        <v>466</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>RPS</v>
       </c>
       <c r="B8">
-        <v>274.32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">

--- a/load-tests/reports/baseline-load-test-report-400.xlsx
+++ b/load-tests/reports/baseline-load-test-report-400.xlsx
@@ -470,7 +470,7 @@
         <v>Avg Response Time (ms)</v>
       </c>
       <c r="B9">
-        <v>12.01</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="10">
@@ -537,7 +537,7 @@
         <v>Average Response Time</v>
       </c>
       <c r="B2">
-        <v>12.01</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="3">
